--- a/qc/TFL-PROGRAMMING-TRACKER.xlsx
+++ b/qc/TFL-PROGRAMMING-TRACKER.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="R4" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-09: Deviation subcategories beyond 'randomised but never dosed' all show 0 (synthetic data has no granular deviation records). Accepted — not a defect.</t>
         </is>
       </c>
       <c r="S4" s="17" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-10: Rows for subsequent anti-cancer therapy + missed assessments show 0 (synthetic data limitation). Accepted — not a defect.</t>
         </is>
       </c>
       <c r="S5" s="17" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="R16" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-06: τ = 30 months (not the SAP-proposed 36 months) bounded by max follow-up. See footnote in t_eff_10_os_rmst.R. Accepted — not a defect.</t>
         </is>
       </c>
       <c r="S16" s="17" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="R17" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-07: PFS-INV ≡ PFS in synthetic data (no separate BICR). Identical results to T-EFF-03 expected. Accepted — not a defect.</t>
         </is>
       </c>
       <c r="S17" s="17" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="R18" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-02 + AL-10: subsequent anti-cancer therapy not simulated; OSWOT censoring applies only the TRTEDT + 30d component. Accepted — not a defect.</t>
         </is>
       </c>
       <c r="S18" s="17" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="R25" s="17" t="inlineStr">
         <is>
-          <t/>
+          <t>AL-08: AESI categorisation uses MedDRA-PT regex stand-in pending SAP §4.6 deferred AESI list. Accepted — not a defect.</t>
         </is>
       </c>
       <c r="S25" s="17" t="inlineStr">

--- a/qc/TFL-PROGRAMMING-TRACKER.xlsx
+++ b/qc/TFL-PROGRAMMING-TRACKER.xlsx
@@ -520,7 +520,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:U39"/>
+  <dimension ref="A1:U44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" bestFit="1" customWidth="1" hidden="false" width="10.711"/>
@@ -706,7 +706,7 @@
       </c>
       <c r="L2" s="16" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M2" s="16" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="L3" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M3" s="17" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="L4" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M4" s="17" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M5" s="17" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="L6" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M6" s="17" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="L7" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M7" s="17" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M8" s="17" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M9" s="17" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M10" s="17" t="inlineStr">
@@ -1669,7 +1669,7 @@
       </c>
       <c r="L11" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M11" s="17" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M12" s="17" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="L13" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M13" s="17" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M14" s="17" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="L15" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M15" s="17" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="L16" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M16" s="17" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="L17" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M17" s="17" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="L18" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M18" s="17" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="L19" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M19" s="17" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="L20" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M20" s="17" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="L21" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M21" s="17" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="L22" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M22" s="17" t="inlineStr">
@@ -2953,7 +2953,7 @@
       </c>
       <c r="L23" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M23" s="17" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="L24" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M24" s="17" t="inlineStr">
@@ -3167,7 +3167,7 @@
       </c>
       <c r="L25" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M25" s="17" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="L26" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M26" s="17" t="inlineStr">
@@ -3381,7 +3381,7 @@
       </c>
       <c r="L27" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M27" s="17" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="L28" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M28" s="17" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="L29" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M29" s="17" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="L30" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M30" s="17" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="L31" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M31" s="17" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="L32" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M32" s="17" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="L33" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M33" s="17" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="L34" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M34" s="17" t="inlineStr">
@@ -4237,7 +4237,7 @@
       </c>
       <c r="L35" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M35" s="17" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="L36" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M36" s="17" t="inlineStr">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="L37" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M37" s="17" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="L38" s="17" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="M38" s="17" t="inlineStr">
@@ -4608,150 +4608,685 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>L-DS-01</t>
         </is>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
         <is>
           <t>listing</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="17" t="inlineStr">
         <is>
           <t>Major Protocol Deviations</t>
         </is>
       </c>
-      <c r="D39" s="18" t="inlineStr">
+      <c r="D39" s="17" t="inlineStr">
         <is>
           <t>ITT</t>
         </is>
       </c>
-      <c r="E39" s="18" t="inlineStr">
+      <c r="E39" s="17" t="inlineStr">
         <is>
           <t>SDTM.DS</t>
         </is>
       </c>
-      <c r="F39" s="18" t="inlineStr">
+      <c r="F39" s="17" t="inlineStr">
         <is>
           <t>shells.yaml + TFL-SHELLS-DOC.docx</t>
         </is>
       </c>
-      <c r="G39" s="18" t="inlineStr">
+      <c r="G39" s="17" t="inlineStr">
         <is>
           <t>programs/tfl/l_ds_01*.R</t>
         </is>
       </c>
-      <c r="H39" s="18" t="inlineStr">
+      <c r="H39" s="17" t="inlineStr">
         <is>
           <t>tfl/tables/L-DS-01.{rtf, docx, html}</t>
         </is>
       </c>
-      <c r="I39" s="18" t="inlineStr">
+      <c r="I39" s="17" t="inlineStr">
         <is>
           <t>§3.2</t>
         </is>
       </c>
-      <c r="J39" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="K39" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="L39" s="18" t="inlineStr">
-        <is>
-          <t>2026-05-16</t>
-        </is>
-      </c>
-      <c r="M39" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="N39" s="18" t="inlineStr">
+      <c r="J39" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K39" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L39" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="M39" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N39" s="17" t="inlineStr">
         <is>
           <t>Independent double programming + footer reconciliation</t>
         </is>
       </c>
-      <c r="O39" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="P39" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="Q39" s="18" t="inlineStr">
+      <c r="O39" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P39" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q39" s="17" t="inlineStr">
         <is>
           <t>Programmed — pending QC</t>
         </is>
       </c>
-      <c r="R39" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="S39" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="T39" s="18" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="U39" s="21" t="inlineStr">
+      <c r="R39" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S39" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T39" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U39" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>T-CM-01</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>Concomitant Medications by Class and Preferred Term</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>SAFETY</t>
+        </is>
+      </c>
+      <c r="E40" s="17" t="inlineStr">
+        <is>
+          <t>ADCM</t>
+        </is>
+      </c>
+      <c r="F40" s="17" t="inlineStr">
+        <is>
+          <t>shells.yaml + TFL-SHELLS-DOC.docx</t>
+        </is>
+      </c>
+      <c r="G40" s="17" t="inlineStr">
+        <is>
+          <t>programs/tfl/t_cm_01*.R</t>
+        </is>
+      </c>
+      <c r="H40" s="17" t="inlineStr">
+        <is>
+          <t>tfl/tables/T-CM-01.{rtf, docx, html}</t>
+        </is>
+      </c>
+      <c r="I40" s="17" t="inlineStr">
+        <is>
+          <t>§5.5</t>
+        </is>
+      </c>
+      <c r="J40" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K40" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L40" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="M40" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N40" s="17" t="inlineStr">
+        <is>
+          <t>Independent double programming + footer reconciliation</t>
+        </is>
+      </c>
+      <c r="O40" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P40" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q40" s="17" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="R40" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S40" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T40" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U40" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="14" t="inlineStr">
+        <is>
+          <t>T-VS-01</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>Vital Signs — Mean Change from Baseline at Key Visits</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>SAFETY</t>
+        </is>
+      </c>
+      <c r="E41" s="17" t="inlineStr">
+        <is>
+          <t>ADVS</t>
+        </is>
+      </c>
+      <c r="F41" s="17" t="inlineStr">
+        <is>
+          <t>shells.yaml + TFL-SHELLS-DOC.docx</t>
+        </is>
+      </c>
+      <c r="G41" s="17" t="inlineStr">
+        <is>
+          <t>programs/tfl/t_vs_01*.R</t>
+        </is>
+      </c>
+      <c r="H41" s="17" t="inlineStr">
+        <is>
+          <t>tfl/tables/T-VS-01.{rtf, docx, html}</t>
+        </is>
+      </c>
+      <c r="I41" s="17" t="inlineStr">
+        <is>
+          <t>§5.5</t>
+        </is>
+      </c>
+      <c r="J41" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K41" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L41" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="M41" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N41" s="17" t="inlineStr">
+        <is>
+          <t>Independent double programming + footer reconciliation</t>
+        </is>
+      </c>
+      <c r="O41" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P41" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q41" s="17" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="R41" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S41" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T41" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U41" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="14" t="inlineStr">
+        <is>
+          <t>T-VS-02</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>Weight Change Categories — Worst On-Treatment % Change</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="inlineStr">
+        <is>
+          <t>SAFETY</t>
+        </is>
+      </c>
+      <c r="E42" s="17" t="inlineStr">
+        <is>
+          <t>ADVS</t>
+        </is>
+      </c>
+      <c r="F42" s="17" t="inlineStr">
+        <is>
+          <t>shells.yaml + TFL-SHELLS-DOC.docx</t>
+        </is>
+      </c>
+      <c r="G42" s="17" t="inlineStr">
+        <is>
+          <t>programs/tfl/t_vs_02*.R</t>
+        </is>
+      </c>
+      <c r="H42" s="17" t="inlineStr">
+        <is>
+          <t>tfl/tables/T-VS-02.{rtf, docx, html}</t>
+        </is>
+      </c>
+      <c r="I42" s="17" t="inlineStr">
+        <is>
+          <t>§5.5</t>
+        </is>
+      </c>
+      <c r="J42" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K42" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L42" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="M42" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N42" s="17" t="inlineStr">
+        <is>
+          <t>Independent double programming + footer reconciliation</t>
+        </is>
+      </c>
+      <c r="O42" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P42" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q42" s="17" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="R42" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S42" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T42" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U42" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="14" t="inlineStr">
+        <is>
+          <t>T-MH-01</t>
+        </is>
+      </c>
+      <c r="B43" s="17" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>Medical History by Category and Term</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>SAFETY</t>
+        </is>
+      </c>
+      <c r="E43" s="17" t="inlineStr">
+        <is>
+          <t>ADMH</t>
+        </is>
+      </c>
+      <c r="F43" s="17" t="inlineStr">
+        <is>
+          <t>shells.yaml + TFL-SHELLS-DOC.docx</t>
+        </is>
+      </c>
+      <c r="G43" s="17" t="inlineStr">
+        <is>
+          <t>programs/tfl/t_mh_01*.R</t>
+        </is>
+      </c>
+      <c r="H43" s="17" t="inlineStr">
+        <is>
+          <t>tfl/tables/T-MH-01.{rtf, docx, html}</t>
+        </is>
+      </c>
+      <c r="I43" s="17" t="inlineStr">
+        <is>
+          <t>§5.5</t>
+        </is>
+      </c>
+      <c r="J43" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K43" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L43" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="M43" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N43" s="17" t="inlineStr">
+        <is>
+          <t>Independent double programming + footer reconciliation</t>
+        </is>
+      </c>
+      <c r="O43" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P43" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q43" s="17" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="R43" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S43" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T43" s="17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U43" s="20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="15" t="inlineStr">
+        <is>
+          <t>T-DV-01</t>
+        </is>
+      </c>
+      <c r="B44" s="18" t="inlineStr">
+        <is>
+          <t>table</t>
+        </is>
+      </c>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>Protocol Deviations — Detail</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>ITT</t>
+        </is>
+      </c>
+      <c r="E44" s="18" t="inlineStr">
+        <is>
+          <t>ADDV</t>
+        </is>
+      </c>
+      <c r="F44" s="18" t="inlineStr">
+        <is>
+          <t>shells.yaml + TFL-SHELLS-DOC.docx</t>
+        </is>
+      </c>
+      <c r="G44" s="18" t="inlineStr">
+        <is>
+          <t>programs/tfl/t_dv_01*.R</t>
+        </is>
+      </c>
+      <c r="H44" s="18" t="inlineStr">
+        <is>
+          <t>tfl/tables/T-DV-01.{rtf, docx, html}</t>
+        </is>
+      </c>
+      <c r="I44" s="18" t="inlineStr">
+        <is>
+          <t>§3.2</t>
+        </is>
+      </c>
+      <c r="J44" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="K44" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="L44" s="18" t="inlineStr">
+        <is>
+          <t>2026-05-17</t>
+        </is>
+      </c>
+      <c r="M44" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="N44" s="18" t="inlineStr">
+        <is>
+          <t>Independent double programming + footer reconciliation</t>
+        </is>
+      </c>
+      <c r="O44" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="P44" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="Q44" s="18" t="inlineStr">
+        <is>
+          <t>Programmed — pending QC</t>
+        </is>
+      </c>
+      <c r="R44" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="S44" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T44" s="18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="U44" s="21" t="inlineStr">
         <is>
           <t/>
         </is>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="Q2:Q39">
+  <conditionalFormatting sqref="Q2:Q44">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="Not started">
       <formula>NOT(ISERROR(SEARCH("Not started", Q2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q39">
+  <conditionalFormatting sqref="Q2:Q44">
     <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Programmed — pending QC">
       <formula>NOT(ISERROR(SEARCH("Programmed — pending QC", Q2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q39">
+  <conditionalFormatting sqref="Q2:Q44">
     <cfRule type="containsText" dxfId="0" priority="3" operator="containsText" text="QC in progress">
       <formula>NOT(ISERROR(SEARCH("QC in progress", Q2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q39">
+  <conditionalFormatting sqref="Q2:Q44">
     <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="QC passed — issues none">
       <formula>NOT(ISERROR(SEARCH("QC passed — issues none", Q2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q39">
+  <conditionalFormatting sqref="Q2:Q44">
     <cfRule type="containsText" dxfId="0" priority="5" operator="containsText" text="QC passed — minor issues resolved">
       <formula>NOT(ISERROR(SEARCH("QC passed — minor issues resolved", Q2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q39">
+  <conditionalFormatting sqref="Q2:Q44">
     <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="QC failed — under rework">
       <formula>NOT(ISERROR(SEARCH("QC failed — under rework", Q2)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q39">
+  <conditionalFormatting sqref="Q2:Q44">
     <cfRule type="containsText" dxfId="0" priority="7" operator="containsText" text="Locked">
       <formula>NOT(ISERROR(SEARCH("Locked", Q2)))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" sqref="Q2:Q39">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="0" sqref="Q2:Q44">
       <formula1>"Not started,Programmed — pending QC,QC in progress,QC passed — issues none,QC passed — minor issues resolved,QC failed — under rework,Locked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4933,7 +5468,7 @@
     <row r="2">
       <c r="A2" s="26" t="inlineStr">
         <is>
-          <t>Generated 2026-05-16 — synthetic data, not for regulatory submission</t>
+          <t>Generated 2026-05-17 — synthetic data, not for regulatory submission</t>
         </is>
       </c>
       <c r="B2" s="16"/>

--- a/qc/TFL-PROGRAMMING-TRACKER.xlsx
+++ b/qc/TFL-PROGRAMMING-TRACKER.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="R4" s="17" t="inlineStr">
         <is>
-          <t>AL-09: Deviation subcategories beyond 'randomised but never dosed' all show 0 (synthetic data has no granular deviation records). Accepted — not a defect.</t>
+          <t/>
         </is>
       </c>
       <c r="S4" s="17" t="inlineStr">
@@ -1057,7 +1057,7 @@
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
-          <t>AL-10: Rows for subsequent anti-cancer therapy + missed assessments show 0 (synthetic data limitation). Accepted — not a defect.</t>
+          <t>AL-10: Subsequent anti-cancer therapy row shows 0 (synthetic CM does not simulate post-trial therapy). Missed-assessments row populated from SDTM.DV as of 2026-05-17. Accepted — not a defect.</t>
         </is>
       </c>
       <c r="S5" s="17" t="inlineStr">

--- a/qc/TFL-PROGRAMMING-TRACKER.xlsx
+++ b/qc/TFL-PROGRAMMING-TRACKER.xlsx
@@ -1057,7 +1057,7 @@
       </c>
       <c r="R5" s="17" t="inlineStr">
         <is>
-          <t>AL-10: Subsequent anti-cancer therapy row shows 0 (synthetic CM does not simulate post-trial therapy). Missed-assessments row populated from SDTM.DV as of 2026-05-17. Accepted — not a defect.</t>
+          <t>AL-12: T-DS-03 IE4 (≥2 consecutive missed tumour assessments) row shows 0 — no gap-detection logic in the synthetic data. Accepted — not a defect.</t>
         </is>
       </c>
       <c r="S5" s="17" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="R17" s="17" t="inlineStr">
         <is>
-          <t>AL-07: PFS-INV ≡ PFS in synthetic data (no separate BICR). Identical results to T-EFF-03 expected. Accepted — not a defect.</t>
+          <t/>
         </is>
       </c>
       <c r="S17" s="17" t="inlineStr">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="R18" s="17" t="inlineStr">
         <is>
-          <t>AL-02 + AL-10: subsequent anti-cancer therapy not simulated; OSWOT censoring applies only the TRTEDT + 30d component. Accepted — not a defect.</t>
+          <t/>
         </is>
       </c>
       <c r="S18" s="17" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="R25" s="17" t="inlineStr">
         <is>
-          <t>AL-08: AESI categorisation uses MedDRA-PT regex stand-in pending SAP §4.6 deferred AESI list. Accepted — not a defect.</t>
+          <t/>
         </is>
       </c>
       <c r="S25" s="17" t="inlineStr">
